--- a/data/Lookup_Tables/Factores.XLSX
+++ b/data/Lookup_Tables/Factores.XLSX
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upcomillas-my.sharepoint.com/personal/mmcamacho_comillas_edu/Documents/Archivos de chat de Microsoft Teams/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beatrizreglero/Desktop/TFG/TFG_Entregas/data/Lookup_Tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEBAF133-EEEA-41CE-AC6B-F073E076786C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{355CEF7E-CDE9-664A-A936-5A75F8DDBEE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{E86B189E-E6A8-446F-B674-C92D512B0498}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="22700" windowHeight="14480" xr2:uid="{E86B189E-E6A8-446F-B674-C92D512B0498}"/>
   </bookViews>
   <sheets>
     <sheet name="Factores" sheetId="1" r:id="rId1"/>
@@ -29,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Clase</t>
   </si>
@@ -48,209 +45,57 @@
     <t>O1</t>
   </si>
   <si>
-    <t>-159,5</t>
-  </si>
-  <si>
-    <t>-100,1</t>
-  </si>
-  <si>
-    <t>101,5</t>
-  </si>
-  <si>
-    <t>31,2</t>
-  </si>
-  <si>
-    <t>134,3</t>
-  </si>
-  <si>
     <t>O2</t>
   </si>
   <si>
-    <t>-242,2</t>
-  </si>
-  <si>
-    <t>-136,3</t>
-  </si>
-  <si>
-    <t>-125,2</t>
-  </si>
-  <si>
-    <t>-128,5</t>
-  </si>
-  <si>
     <t>O3</t>
   </si>
   <si>
-    <t>-82,71</t>
-  </si>
-  <si>
-    <t>317,9</t>
-  </si>
-  <si>
-    <t>173,6</t>
-  </si>
-  <si>
     <t>P1</t>
   </si>
   <si>
-    <t>263,5</t>
-  </si>
-  <si>
-    <t>26,17</t>
-  </si>
-  <si>
-    <t>128,7</t>
-  </si>
-  <si>
-    <t>112,4</t>
-  </si>
-  <si>
-    <t>-69,98</t>
-  </si>
-  <si>
     <t>P2</t>
   </si>
   <si>
-    <t>88,31</t>
-  </si>
-  <si>
-    <t>179,7</t>
-  </si>
-  <si>
-    <t>363,7</t>
-  </si>
-  <si>
-    <t>188,1</t>
-  </si>
-  <si>
     <t>E1</t>
   </si>
   <si>
-    <t>-266,7</t>
-  </si>
-  <si>
-    <t>-68,23</t>
-  </si>
-  <si>
-    <t>41,97</t>
-  </si>
-  <si>
-    <t>-143,4</t>
-  </si>
-  <si>
     <t>E2</t>
   </si>
   <si>
-    <t>-183,5</t>
-  </si>
-  <si>
-    <t>-95,06</t>
-  </si>
-  <si>
-    <t>2,12</t>
-  </si>
-  <si>
     <t>J1</t>
   </si>
   <si>
-    <t>-54,94</t>
-  </si>
-  <si>
-    <t>93,55</t>
-  </si>
-  <si>
-    <t>176,9</t>
-  </si>
-  <si>
-    <t>376,1</t>
-  </si>
-  <si>
-    <t>54,59</t>
-  </si>
-  <si>
     <t>J2</t>
   </si>
   <si>
-    <t>123,1</t>
-  </si>
-  <si>
-    <t>116,4</t>
-  </si>
-  <si>
-    <t>165,4</t>
-  </si>
-  <si>
     <t>Pe1</t>
   </si>
   <si>
-    <t>83,52</t>
-  </si>
-  <si>
-    <t>21,23</t>
-  </si>
-  <si>
-    <t>173,9</t>
-  </si>
-  <si>
-    <t>416,2</t>
-  </si>
-  <si>
     <t>Pe2</t>
   </si>
   <si>
-    <t>95,24</t>
-  </si>
-  <si>
-    <t>104,5</t>
-  </si>
-  <si>
-    <t>206,3</t>
-  </si>
-  <si>
     <t>C</t>
   </si>
   <si>
-    <t>224,3</t>
-  </si>
-  <si>
-    <t>170,6</t>
-  </si>
-  <si>
-    <t>219,7</t>
-  </si>
-  <si>
-    <t>230,7</t>
-  </si>
-  <si>
-    <t>218,3</t>
-  </si>
-  <si>
     <t>X</t>
-  </si>
-  <si>
-    <t>-138,5</t>
-  </si>
-  <si>
-    <t>-278,6</t>
-  </si>
-  <si>
-    <t>-370,6</t>
-  </si>
-  <si>
-    <t>-430,6</t>
-  </si>
-  <si>
-    <t>40,46</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -278,7 +123,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -297,9 +142,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -337,7 +182,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -443,7 +288,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -585,7 +430,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -594,9 +439,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{890C4467-1F14-4397-9A34-F05E3341A640}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -616,264 +461,264 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1">
+        <v>-159.5</v>
+      </c>
+      <c r="C3" s="1">
+        <v>-100.1</v>
+      </c>
+      <c r="D3" s="1">
+        <v>101.5</v>
+      </c>
+      <c r="E3" s="1">
+        <v>31.2</v>
+      </c>
+      <c r="F3" s="1">
+        <v>134.30000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B4" s="1">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1">
+        <v>-242.2</v>
+      </c>
+      <c r="D4" s="1">
+        <v>-136.30000000000001</v>
+      </c>
+      <c r="E4" s="1">
+        <v>-125.2</v>
+      </c>
+      <c r="F4" s="1">
+        <v>-128.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B5" s="1">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1">
+        <v>-82.71</v>
+      </c>
+      <c r="E5" s="1">
+        <v>317.89999999999998</v>
+      </c>
+      <c r="F5" s="1">
+        <v>173.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="E3" t="s">
+      <c r="B6" s="1">
+        <v>263.5</v>
+      </c>
+      <c r="C6" s="1">
+        <v>26.17</v>
+      </c>
+      <c r="D6" s="1">
+        <v>128.69999999999999</v>
+      </c>
+      <c r="E6" s="1">
+        <v>112.4</v>
+      </c>
+      <c r="F6" s="1">
+        <v>-69.98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
+      <c r="B7" s="1">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1">
+        <v>88.31</v>
+      </c>
+      <c r="D7" s="1">
+        <v>179.7</v>
+      </c>
+      <c r="E7" s="1">
+        <v>363.7</v>
+      </c>
+      <c r="F7" s="1">
+        <v>188.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="B8" s="1">
+        <v>-266.7</v>
+      </c>
+      <c r="C8" s="1">
+        <v>-68.23</v>
+      </c>
+      <c r="D8" s="1">
+        <v>-2.3929999999999998</v>
+      </c>
+      <c r="E8" s="1">
+        <v>41.97</v>
+      </c>
+      <c r="F8" s="1">
+        <v>-143.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B4">
+      <c r="B9" s="1">
         <v>0</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C9" s="1">
+        <v>-439</v>
+      </c>
+      <c r="D9" s="1">
+        <v>-183.5</v>
+      </c>
+      <c r="E9" s="1">
+        <v>-95.06</v>
+      </c>
+      <c r="F9" s="1">
+        <v>2.12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="D4" t="s">
+      <c r="B10" s="1">
+        <v>-54.94</v>
+      </c>
+      <c r="C10" s="1">
+        <v>93.55</v>
+      </c>
+      <c r="D10" s="1">
+        <v>176.9</v>
+      </c>
+      <c r="E10" s="1">
+        <v>376.1</v>
+      </c>
+      <c r="F10" s="1">
+        <v>54.59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="E4" t="s">
+      <c r="B11" s="1">
+        <v>0</v>
+      </c>
+      <c r="C11" s="1">
+        <v>123.1</v>
+      </c>
+      <c r="D11" s="1">
+        <v>116.4</v>
+      </c>
+      <c r="E11" s="1">
+        <v>204</v>
+      </c>
+      <c r="F11" s="1">
+        <v>165.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="F4" t="s">
+      <c r="B12" s="1">
+        <v>83.52</v>
+      </c>
+      <c r="C12" s="1">
+        <v>21.23</v>
+      </c>
+      <c r="D12" s="1">
+        <v>173.9</v>
+      </c>
+      <c r="E12" s="1">
+        <v>365</v>
+      </c>
+      <c r="F12" s="1">
+        <v>416.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+      <c r="B13" s="1">
+        <v>9.2880000000000003</v>
+      </c>
+      <c r="C13" s="1">
+        <v>95.24</v>
+      </c>
+      <c r="D13" s="1">
+        <v>104.5</v>
+      </c>
+      <c r="E13" s="1">
+        <v>206.3</v>
+      </c>
+      <c r="F13" s="1">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="B14" s="1">
+        <v>224.3</v>
+      </c>
+      <c r="C14" s="1">
+        <v>170.6</v>
+      </c>
+      <c r="D14" s="1">
+        <v>219.7</v>
+      </c>
+      <c r="E14" s="1">
+        <v>230.7</v>
+      </c>
+      <c r="F14" s="1">
+        <v>218.3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="1">
-        <v>-2393</v>
-      </c>
-      <c r="E8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>-439</v>
-      </c>
-      <c r="D9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11">
-        <v>204</v>
-      </c>
-      <c r="F11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12">
-        <v>365</v>
-      </c>
-      <c r="F12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" s="1">
-        <v>9288</v>
-      </c>
-      <c r="C13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>56</v>
-      </c>
-      <c r="B14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" t="s">
-        <v>65</v>
-      </c>
-      <c r="E15" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" t="s">
-        <v>67</v>
+      <c r="B15" s="1">
+        <v>-138.5</v>
+      </c>
+      <c r="C15" s="1">
+        <v>-278.60000000000002</v>
+      </c>
+      <c r="D15" s="1">
+        <v>-370.6</v>
+      </c>
+      <c r="E15" s="1">
+        <v>-430.6</v>
+      </c>
+      <c r="F15" s="1">
+        <v>40.46</v>
       </c>
     </row>
   </sheetData>
@@ -882,6 +727,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008CC35A7A26A4324F8F38BD84F25AF9C1" ma:contentTypeVersion="7" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="b819923d2297222e9ee10f9e0fee1a03">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b193dfaa-deae-48b4-a85f-1fcd6ead3755" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="db138671d8e145de4e330d26d84748c1" ns2:_="">
     <xsd:import namespace="b193dfaa-deae-48b4-a85f-1fcd6ead3755"/>
@@ -1043,29 +903,37 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC85A426-CE1B-4F91-8F01-858ABEBDDDB9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71F311C0-9573-4B98-885D-B0C8F8CFF375}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52C2F5D5-4865-4008-861F-10FF31B259C2}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71F311C0-9573-4B98-885D-B0C8F8CFF375}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC85A426-CE1B-4F91-8F01-858ABEBDDDB9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52C2F5D5-4865-4008-861F-10FF31B259C2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b193dfaa-deae-48b4-a85f-1fcd6ead3755"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>